--- a/experiment/DAT_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/DAT_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.05</v>
+        <v>23.06</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5347</v>
+        <v>0.5356</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.94</v>
+        <v>26.07</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7512</v>
+        <v>0.7544</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>25.42</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6374</v>
+        <v>0.6378</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.32</v>
+        <v>26.3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5802</v>
+        <v>0.5790999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.61</v>
+        <v>23.63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7352</v>
+        <v>0.7369</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.92</v>
+        <v>32.94</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7955</v>
+        <v>0.7959000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.32</v>
+        <v>28.37</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.8214</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.84</v>
+        <v>33.92</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9205</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.62</v>
+        <v>32.63</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8667</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.38</v>
+        <v>27.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7507</v>
+        <v>0.7513</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.97</v>
+        <v>33.05</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9447</v>
+        <v>0.9453</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.23</v>
+        <v>34.27</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8801</v>
+        <v>0.8804999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.53</v>
+        <v>26.55</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9449</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.43</v>
+        <v>27.48</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7792</v>
+        <v>0.7798</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.61</v>
+        <v>28.65</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7815</v>
+        <v>0.7822</v>
       </c>
     </row>
   </sheetData>
